--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_500_Montserrat_UK.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_500_Montserrat_UK.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R3d20fe4b68424f57"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R5592d8ca6b4a4616"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R7c95eeef76434a8d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R84630afd211d45e9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="Rdeb76b79735743ef"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="Re96b239d4b124238"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R69d8153dcc364f8b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Re0b4ec38559f4bc4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R2b8ca9d11e6741cf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R9ce57dccea134a25"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R9fd9c0e5ba6d44f2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R103f3dbc91644580"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ500CommercialTable" displayName="EEZ500CommercialTable" ref="A1:O7" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O7"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ500CommercialTable" displayName="EEZ500CommercialTable" ref="A1:E7" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E7"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ500FunctionalTable" displayName="EEZ500FunctionalTable" ref="A1:O13" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O13"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ500FunctionalTable" displayName="EEZ500FunctionalTable" ref="A1:E13" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E13"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ500ValidationTable" displayName="EEZ500ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ500ValidationTable" displayName="EEZ500ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -6523,7 +6477,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8e385eeb4821449c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R78ab61c80bf44f14"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6533,20 +6487,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -6554,390 +6498,136 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>0.33088837899999995</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.2003656971585586</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>158.622831195193</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>0.33088837899999995</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>159.30023701804558</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$88,A2,'Species'!$U$2:$U$88))</x:f>
-        <x:v>52.710597201216885</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.2003656971585586</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>158.622831195193</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>52.486451486568036</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>0.22414571464884858</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0042705442700048</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.00427054427000481</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>0.039552592</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.16</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>144.5439770745928</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>0.039552592</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>144.5439770745928</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$88,A3,'Species'!$U$2:$U$88))</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>5.717088951288722</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.16</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>144.5439770745928</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
-        <x:v>5.717088951288722</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>24.703644711</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.254648520063878</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>179.74156554400545</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>24.703644711</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>188.65424060632685</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$88,A4,'Species'!$U$2:$U$88))</x:f>
-        <x:v>4660.4473331622075</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.254648520063878</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>179.74156554400545</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>4440.27177499803</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>220.17555816417735</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0495860544852067</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.0495860544852066</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>20.817868976</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.8082216693018545</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>643.0158368475822</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>20.817868976</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>1382.3627745359026</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$88,A5,'Species'!$U$2:$U$88))</x:f>
-        <x:v>28777.847117588248</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.8082216693018545</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>643.0158368475822</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>13386.21944098596</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>15391.627676602287</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>2.1498113970458426</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>1.1498113970458428</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>0.182091043</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.2377774030323945</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>1728.929971682907</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>0.182091043</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>1775.7492594286648</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$88,A6,'Species'!$U$2:$U$88))</x:f>
-        <x:v>323.3480347558432</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.2377774030323945</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>1728.929971682907</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>314.82266181770103</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>8.52537293814214</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0270799214037483</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.02707992140374819</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>3.338604712</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>4.344775678544002</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>2211.9518987741103</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>3.338604712</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>2216.3870530942518</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$88,A7,'Species'!$U$2:$U$88))</x:f>
-        <x:v>7399.640259076263</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>4.344775678544002</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>2211.9518987741103</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>7384.833031964592</x:v>
       </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>14.807227111670727</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.0020050862419745</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.002005086241974458</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G7">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O7">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R711f298cb63343db"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R664e95e64e7449ff"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6947,20 +6637,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -6968,714 +6648,250 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>0.017333039</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>4.5</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>3162.2776601683795</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>0.017333039</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>3162.2776601683795</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$88,A2,'Species'!$U$2:$U$88))</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>54.81188201252727</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>4.5</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>3162.2776601683795</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
-        <x:v>54.81188201252727</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>13.361131400000001</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.347701186656244</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>2226.9024170819876</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>13.361131400000001</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>2248.151974555685</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$88,A3,'Species'!$U$2:$U$88))</x:f>
-        <x:v>30037.853939207966</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.347701186656244</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>2226.9024170819876</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>29753.935809610044</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>283.9181295979215</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.0095422041445092</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.009542204144509195</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>0.32186536300000007</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.036504492470039</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>1087.6883889418716</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>0.32186536300000007</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>1634.458155096548</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$88,A4,'Species'!$U$2:$U$88))</x:f>
-        <x:v>526.0754673984608</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.036504492470039</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>1087.6883889418716</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>350.0892181376608</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>175.98624926079998</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.5026897149160399</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.5026897149160399</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>0.182091043</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.2377774030323945</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>1728.929971682907</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>0.182091043</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>1775.7492594286648</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$88,A5,'Species'!$U$2:$U$88))</x:f>
-        <x:v>323.3480347558432</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.2377774030323945</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>1728.929971682907</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>314.82266181770103</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>8.52537293814214</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0270799214037483</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.02707992140374819</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>0.33088837899999995</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.2003656971585586</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>158.622831195193</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>0.33088837899999995</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>159.30023701804558</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$88,A6,'Species'!$U$2:$U$88))</x:f>
-        <x:v>52.710597201216885</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.2003656971585586</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>158.622831195193</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>52.486451486568036</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>0.22414571464884858</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0042705442700048</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.00427054427000481</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Medium bathydemersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>0.067801854</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>4.18</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>1513.5612484362073</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>0.067801854</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>1513.5612484362073</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$88,A7,'Species'!$U$2:$U$88))</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>102.62225878652944</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>4.18</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>1513.5612484362073</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
-        <x:v>102.62225878652944</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>0.0050371289999999996</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>4.166645122648238</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>1467.7264564042</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>0.0050371289999999996</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>1593.0024741812992</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$88,A8,'Species'!$U$2:$U$88))</x:f>
-        <x:v>8.024158959770373</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>4.166645122648238</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>1467.7264564042</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>7.3931274976208305</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>0.6310314621495428</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.0853537913897215</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.08535379138972159</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>20.110189190999996</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.2747696029822992</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>188.26500622074764</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>20.110189190999996</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>190.7797159192282</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$88,A9,'Species'!$U$2:$U$88))</x:f>
-        <x:v>3836.616180940913</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.2747696029822992</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>188.26500622074764</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>3786.044893144026</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>50.57128779688719</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.0133572868849137</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.0133572868849137</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>2.260016438</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.149376531848925</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>141.05111768724777</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>2.260016438</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>223.14032788707652</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$88,A10,'Species'!$U$2:$U$88))</x:f>
-        <x:v>504.30080900550274</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.149376531848925</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>141.05111768724777</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>318.77784457145253</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>185.5229644340502</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.58198199025863</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.5819819902586302</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>8.754156380000001</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.531018501153391</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>339.63974109822203</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>8.754156380000001</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>596.3282569968503</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$88,A11,'Species'!$U$2:$U$88))</x:f>
-        <x:v>5220.350815563258</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.531018501153391</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>339.63974109822203</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>2973.259406436549</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>2247.091409126709</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.7557670226358917</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.7557670226358917</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>0.039552592</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.16</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>144.5439770745928</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>0.039552592</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>144.5439770745928</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$88,A12,'Species'!$U$2:$U$88))</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>5.717088951288722</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.16</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>144.5439770745928</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
-        <x:v>5.717088951288722</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>3.962587605</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>2.6572146081348276</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>45.416598891787956</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>3.962587605</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>138.11157064672292</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$88,A13,'Species'!$U$2:$U$88))</x:f>
-        <x:v>547.279197951786</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>2.6572146081348276</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>45.416598891787956</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>179.96725182985568</x:v>
       </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>367.31194612193036</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>3.040993249534053</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>2.040993249534053</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G13">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O13">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R13a8860c175743bf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2b78c6d070b8436a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7850,7 +7066,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -7949,7 +7165,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>41219.71043073505</x:v>
+        <x:v>25584.35045020414</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -7963,7 +7179,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>41219.71043073505</x:v>
+        <x:v>37899.92789428181</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -7977,7 +7193,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>-7.275957614183426e-12</x:v>
+        <x:v>-15635.35998053092</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -7991,7 +7207,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>-7.275957614183426e-12</x:v>
+        <x:v>-3319.7825364532473</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -8002,9 +7218,9 @@
         <x:v>EEZ_500</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -8016,47 +7232,19 @@
         <x:v>EEZ_500</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_500</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_500</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2aa2df4403294153"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R59514c5e04114c14"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8103,7 +7291,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
